--- a/business_forms/045_office_relocation_delivery_form--business_forms.xlsx
+++ b/business_forms/045_office_relocation_delivery_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>delivery_information</t>
+          <t>Delivery Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>delivery_method</t>
+          <t>Delivery Method</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,23 +561,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>delivery_instructions</t>
+          <t>delivery_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>delivery_instructions</t>
+          <t>Delivery Status</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>office_id</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>Office ID</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>item_details</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>item_details</t>
+          <t>Item ID</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>delivery_schedule</t>
+          <t>Delivery Schedule</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>delivery_time</t>
+          <t>Delivery Time</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>delivery_date</t>
+          <t>Delivery Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>remarks</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>contact_details</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Contact Details</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>delivery_personnel_details</t>
+          <t>Delivery Personnel Details</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>delivery_status</t>
+          <t>delivery_personnel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>delivery_status</t>
+          <t>Delivery Personnels</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>office_id</t>
+          <t>delivery_notes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>office_id</t>
+          <t>Delivery Notes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>delivery_status_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>Delivery Status 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>remarks_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>Remarks 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>delivery_method</t>
+          <t>delivery_method_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>delivery_method</t>
+          <t>Delivery Method 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>delivery_instructions</t>
+          <t>delivery_notes_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>delivery_instructions</t>
+          <t>Delivery Notes 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>item_details</t>
+          <t>Item Details</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>contact_details_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>Contact Details 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>delivery_status</t>
+          <t>delivery_status_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>delivery_status</t>
+          <t>Delivery Status 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>delivery_notes</t>
+          <t>delivery_personnel_details_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>delivery_notes</t>
+          <t>Delivery Personnels Details</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>delivery_personnel_details</t>
+          <t>remarks_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>delivery_personnel_details</t>
+          <t>Remarks 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>remarks</t>
+          <t>office_id_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>remarks</t>
+          <t>Office Id 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1075,12 +1075,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'delivery_method',_'label':_'delivery_method',_'value':_'delivery_method'}</t>
+          <t>delivery_method</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'delivery_method', 'label': 'delivery_method', 'value': 'delivery_method'}</t>
+          <t>Delivery Method</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pick_up',_'label':_'pick_up',_'value':_'pick_up'}</t>
+          <t>pick_up</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'pick_up', 'label': 'pick_up', 'value': 'pick_up'}</t>
+          <t>Pick up</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'courier',_'label':_'courier',_'value':_'courier'}</t>
+          <t>courier</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'courier', 'label': 'courier', 'value': 'courier'}</t>
+          <t>Courier</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'drop_off',_'label':_'drop_off',_'value':_'drop_off'}</t>
+          <t>drop_off</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'drop_off', 'label': 'drop_off', 'value': 'drop_off'}</t>
+          <t>Drop off</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'delivery_personnel',_'label':_'delivery_personnel',_'value':_'delivery_personnel'}</t>
+          <t>delivery_personnel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'delivery_personnel', 'label': 'delivery_personnel', 'value': 'delivery_personnel'}</t>
+          <t>Delivery Personnel</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'delivered',_'label':_'delivered',_'value':_'delivered'}</t>
+          <t>delivered</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'delivered', 'label': 'delivered', 'value': 'delivered'}</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pending',_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'pending', 'label': 'pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'completed',_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'completed', 'label': 'completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1244,165 +1244,233 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'cancelled',_'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'cancelled', 'label': 'cancelled', 'value': 'cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>delivery_method_choices</t>
+          <t>delivery_status_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'delivery_method',_'label':_'delivery_method',_'value':_'delivery_method'}</t>
+          <t>delivered</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'delivery_method', 'label': 'delivery_method', 'value': 'delivery_method'}</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>delivery_method_choices</t>
+          <t>delivery_status_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pick_up',_'label':_'pick_up',_'value':_'pick_up'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'pick_up', 'label': 'pick_up', 'value': 'pick_up'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>delivery_method_choices</t>
+          <t>delivery_status_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'courier',_'label':_'courier',_'value':_'courier'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'courier', 'label': 'courier', 'value': 'courier'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>delivery_method_choices</t>
+          <t>delivery_status_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'drop_off',_'label':_'drop_off',_'value':_'drop_off'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'drop_off', 'label': 'drop_off', 'value': 'drop_off'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>delivery_method_choices</t>
+          <t>delivery_method_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'delivery_personnel',_'label':_'delivery_personnel',_'value':_'delivery_personnel'}</t>
+          <t>delivery_method</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'delivery_personnel', 'label': 'delivery_personnel', 'value': 'delivery_personnel'}</t>
+          <t>Delivery Method</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>delivery_method_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'delivered',_'label':_'delivered',_'value':_'delivered'}</t>
+          <t>pick_up</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'delivered', 'label': 'delivered', 'value': 'delivered'}</t>
+          <t>Pick up</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>delivery_method_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pending',_'label':_'pending',_'value':_'pending'}</t>
+          <t>courier</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'pending', 'label': 'pending', 'value': 'pending'}</t>
+          <t>Courier</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>delivery_method_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'completed',_'label':_'completed',_'value':_'completed'}</t>
+          <t>drop_off</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'completed', 'label': 'completed', 'value': 'completed'}</t>
+          <t>Drop off</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>delivery_method_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'cancelled',_'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>delivery_personnel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'cancelled', 'label': 'cancelled', 'value': 'cancelled'}</t>
+          <t>Delivery Personnel</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>delivered</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>delivery_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>delivery_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>delivery_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
